--- a/Tools/Luban/DataTables/Datas/物品_Item.xlsx
+++ b/Tools/Luban/DataTables/Datas/物品_Item.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Tools/Luban/DataTables/Datas/物品_Item.xlsx
+++ b/Tools/Luban/DataTables/Datas/物品_Item.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,6 +484,11 @@
           <t>descKey</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>iconSprite</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -515,6 +521,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -545,6 +556,11 @@
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>描述key</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>图标sprite名</t>
         </is>
       </c>
     </row>
@@ -571,6 +587,11 @@
           <t>item_1001_desc</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -595,6 +616,11 @@
           <t>item_1002_desc</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -619,6 +645,11 @@
           <t>item_1003_desc</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SL_Item_c2_r0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -643,6 +674,11 @@
           <t>item_2001_desc</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r3</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -667,6 +703,11 @@
           <t>item_2002_desc</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -691,6 +732,11 @@
           <t>item_2003_desc</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SL_Item_c2_r3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -715,6 +761,11 @@
           <t>item_2004_desc</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SL_Item_c3_r3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -739,6 +790,11 @@
           <t>item_2005_desc</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SL_Item_c4_r3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -763,6 +819,11 @@
           <t>item_3001_desc</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r6</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -787,6 +848,11 @@
           <t>item_3002_desc</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r6</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -811,6 +877,11 @@
           <t>item_3003_desc</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SL_Item_c2_r6</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -835,6 +906,11 @@
           <t>item_3004_desc</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SL_Item_c3_r6</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -859,6 +935,11 @@
           <t>item_3005_desc</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SL_Item_c4_r6</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -883,6 +964,11 @@
           <t>item_3101_desc</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SL_Item_c5_r6</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -907,6 +993,11 @@
           <t>item_3006_desc</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SL_Item_c6_r6</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -931,6 +1022,11 @@
           <t>item_3007_desc</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SL_Item_c7_r6</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -955,6 +1051,11 @@
           <t>item_4001_desc</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r9</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -979,6 +1080,11 @@
           <t>item_4002_desc</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r9</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1003,6 +1109,11 @@
           <t>item_4003_desc</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>SL_Item_c2_r9</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1027,6 +1138,11 @@
           <t>item_4004_desc</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SL_Item_c3_r9</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1051,6 +1167,11 @@
           <t>item_5001_desc</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SL_Item_c0_r12</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1075,6 +1196,11 @@
           <t>item_5002_desc</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SL_Item_c1_r12</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1099,6 +1225,11 @@
           <t>item_5003_desc</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SL_Item_c2_r12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1123,6 +1254,11 @@
           <t>item_5004_desc</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SL_Item_c3_r12</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1147,6 +1283,11 @@
           <t>item_5005_desc</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SL_Item_c4_r12</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1171,6 +1312,11 @@
           <t>item_9001_desc</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SL_Item_c7_r14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
